--- a/data/externalStats/File1/RPT_RPT4864512660729AG_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT4864512660729AG_externalStats.xlsx
@@ -4007,13 +4007,13 @@
         <v>11377.65923837764</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3422.487711428827</v>
+        <v>3422.487711428825</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36460.87458884433</v>
+        <v>36460.87458884434</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23326.03531108902</v>
@@ -4022,13 +4022,13 @@
         <v>12035.45165849652</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3876.170523329413</v>
+        <v>3876.170523329414</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>39237.65749291496</v>
+        <v>39237.65749291495</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -4313,10 +4313,10 @@
         <v>2594.410828881019</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>985.1537316312744</v>
+        <v>985.1537316312742</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.8945333813836</v>
+        <v>255.8945333813835</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -4328,10 +4328,10 @@
         <v>2524.098090035487</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.4907245728978</v>
+        <v>955.490724572898</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3325380336441</v>
+        <v>249.3325380336442</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -4343,16 +4343,16 @@
         <v>2448.763529811295</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>923.9759324905136</v>
+        <v>923.9759324905137</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>242.2889407543105</v>
+        <v>242.2889407543106</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.028403056119</v>
+        <v>3615.02840305612</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>32.36265349002131</v>
@@ -4646,13 +4646,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>5.09858052922456</v>
@@ -4664,7 +4664,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>30.28909928964937</v>
@@ -4715,10 +4715,10 @@
         <v>18137</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5479.249428155603</v>
+        <v>5479.249428155596</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1629.268768588716</v>
+        <v>1629.268768588714</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>579.6662951627213</v>
@@ -4727,31 +4727,31 @@
         <v>17013.70034841627</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>24701.88484032331</v>
+        <v>24701.8848403233</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>603.5533808446435</v>
+        <v>603.5533808446448</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>18677.29304011532</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>26698.52652119438</v>
+        <v>26698.52652119437</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6021.326513823609</v>
+        <v>6021.326513823606</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20543.90331686658</v>
@@ -4771,7 +4771,7 @@
         <v>880391.1703553336</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>2705.748534253711</v>
+        <v>2705.748534253712</v>
       </c>
     </row>
     <row r="64">
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>490934.3341392858</v>
+        <v>490934.3341392857</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2589.08465126051</v>
@@ -5168,7 +5168,7 @@
         <v>20543.90331686658</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>90775.05061180433</v>
+        <v>90775.0506118043</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5415,10 +5415,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>89.47329720611964</v>
+        <v>89.47329720611963</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>54.7544447970989</v>
+        <v>54.75444479709891</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>13.17974339598205</v>
@@ -5436,7 +5436,7 @@
         <v>48.60500608217873</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>8.711605480314148</v>
+        <v>8.71160548031415</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>5.689968476792075</v>
@@ -5537,10 +5537,10 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -5549,10 +5549,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N74" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>12.14013438652261</v>
@@ -5567,7 +5567,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V74" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W74" s="131" t="n">
         <v>8.002227321906959</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>144.6208709956583</v>
@@ -5671,7 +5671,7 @@
         <v>167</v>
       </c>
       <c r="J76" s="130" t="n">
-        <v>107.034058846203</v>
+        <v>107.0340588462029</v>
       </c>
       <c r="K76" s="131" t="n">
         <v>28.64956631726437</v>
@@ -6006,7 +6006,7 @@
         <v>2397</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>0</v>
@@ -6015,13 +6015,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
@@ -6036,10 +6036,10 @@
         <v>2915.326833312611</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>9.932555049414749</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3180.836645549764</v>
+        <v>3180.836645549763</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>5357.161593511445</v>
+        <v>5357.161593511444</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6608,7 +6608,7 @@
         <v>32117</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>20536.86719694407</v>
+        <v>20536.86719694408</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>10920.07550760238</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>34569.77122015016</v>
+        <v>34569.77122015017</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>21715.48208383497</v>
@@ -6629,7 +6629,7 @@
         <v>11390.83898177362</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3431.616244730875</v>
+        <v>3431.616244730874</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>23374.6403171712</v>
       </c>
       <c r="W90" s="131" t="n">
-        <v>12044.16326397684</v>
+        <v>12044.16326397683</v>
       </c>
       <c r="X90" s="131" t="n">
         <v>3881.860491806206</v>
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>39300.66407295424</v>
+        <v>39300.66407295423</v>
       </c>
     </row>
     <row r="91">
@@ -6742,10 +6742,10 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -6754,10 +6754,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N92" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>12.14013438652261</v>
@@ -6772,7 +6772,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V92" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W92" s="131" t="n">
         <v>8.002227321906959</v>
@@ -6781,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>144.6208709956583</v>
@@ -6882,7 +6882,7 @@
         <v>1013.803297948539</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>264.3214736883766</v>
+        <v>264.3214736883765</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>2624.318142957748</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>978.1421914832281</v>
+        <v>978.1421914832283</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>255.9861033440639</v>
+        <v>255.986103344064</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -6909,10 +6909,10 @@
         <v>2540.109190153185</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>939.3625222898573</v>
+        <v>939.3625222898575</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>246.5315273269332</v>
+        <v>246.5315273269333</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -7144,7 +7144,7 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>32.36265349002131</v>
@@ -7156,13 +7156,13 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>5.09858052922456</v>
@@ -7174,7 +7174,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>30.28909928964937</v>
@@ -7211,28 +7211,28 @@
         <v>20534</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5479.249428155606</v>
+        <v>5479.249428155599</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1629.268768588718</v>
+        <v>1629.268768588716</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>579.6662951627213</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>19682.11874075477</v>
+        <v>19682.11874075476</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>27370.30323266181</v>
+        <v>27370.3032326618</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>603.553380844643</v>
+        <v>603.5533808446444</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>21592.61987342794</v>
@@ -7241,19 +7241,19 @@
         <v>29613.85335450699</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6021.326513823606</v>
+        <v>6021.326513823602</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>23717.12306039543</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>32111.86101883307</v>
+        <v>32111.86101883306</v>
       </c>
     </row>
     <row r="100">
@@ -7562,7 +7562,7 @@
         <v>19690.79668663907</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>83149.83858095342</v>
+        <v>83149.83858095339</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>30269.455562463</v>
@@ -7580,7 +7580,7 @@
         <v>89020.12021794211</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>32116.05364128187</v>
+        <v>32116.05364128186</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>14764.98862398453</v>
@@ -7589,10 +7589,10 @@
         <v>4763.557007817432</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>23724.73996241635</v>
+        <v>23724.73996241634</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>96132.21220531575</v>
+        <v>96132.21220531574</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>36479108.3909279</v>
+        <v>36479108.39092791</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>47681.20374516814</v>
+        <v>47681.20374516815</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8705,7 +8705,7 @@
         <v>11661398.77421439</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>13973.95203328433</v>
+        <v>13973.95203328434</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -9455,7 +9455,7 @@
         <v>1696818.117976401</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>3262.52226153056</v>
+        <v>3262.522261530559</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>9752260.17393212</v>
+        <v>9752260.173932118</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>11809.35136079674</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6687841.894400667</v>
+        <v>6687841.894400666</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>987.4975766638678</v>
@@ -10531,13 +10531,13 @@
         <v>11377.65923837764</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3422.487711428827</v>
+        <v>3422.487711428825</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36460.87458884433</v>
+        <v>36460.87458884434</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23326.03531108902</v>
@@ -10546,13 +10546,13 @@
         <v>12035.45165849652</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3876.170523329413</v>
+        <v>3876.170523329414</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>39237.65749291496</v>
+        <v>39237.65749291495</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>2377596.98587188</v>
+        <v>2377596.985871879</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>590.0148331949123</v>
@@ -10837,10 +10837,10 @@
         <v>2594.410828881019</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>985.1537316312744</v>
+        <v>985.1537316312742</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.8945333813836</v>
+        <v>255.8945333813835</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -10852,10 +10852,10 @@
         <v>2524.098090035487</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.4907245728978</v>
+        <v>955.490724572898</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3325380336441</v>
+        <v>249.3325380336442</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -10867,16 +10867,16 @@
         <v>2448.763529811295</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>923.9759324905136</v>
+        <v>923.9759324905137</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>242.2889407543105</v>
+        <v>242.2889407543106</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.028403056119</v>
+        <v>3615.02840305612</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10890,7 +10890,7 @@
         <v>1437144.675930581</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>3529.071372179999</v>
+        <v>3529.07137218</v>
       </c>
     </row>
     <row r="59">
@@ -11158,7 +11158,7 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>32.36265349002131</v>
@@ -11170,13 +11170,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>5.09858052922456</v>
@@ -11188,7 +11188,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>30.28909928964937</v>
@@ -11239,10 +11239,10 @@
         <v>18137</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5479.249428155603</v>
+        <v>5479.249428155596</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1629.268768588716</v>
+        <v>1629.268768588714</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>579.6662951627213</v>
@@ -11251,31 +11251,31 @@
         <v>17013.70034841627</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>24701.88484032331</v>
+        <v>24701.8848403233</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>603.5533808446435</v>
+        <v>603.5533808446448</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>18677.29304011532</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>26698.52652119438</v>
+        <v>26698.52652119437</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6021.326513823609</v>
+        <v>6021.326513823606</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20543.90331686658</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11692,7 +11692,7 @@
         <v>20543.90331686658</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>90775.05061180433</v>
+        <v>90775.0506118043</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11939,10 +11939,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>89.47329720611964</v>
+        <v>89.47329720611963</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>54.7544447970989</v>
+        <v>54.75444479709891</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>13.17974339598205</v>
@@ -11960,7 +11960,7 @@
         <v>48.60500608217873</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>8.711605480314148</v>
+        <v>8.71160548031415</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>5.689968476792075</v>
@@ -12061,10 +12061,10 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -12073,10 +12073,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N74" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>12.14013438652261</v>
@@ -12091,7 +12091,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V74" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W74" s="131" t="n">
         <v>8.002227321906959</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>144.6208709956583</v>
@@ -12195,7 +12195,7 @@
         <v>167</v>
       </c>
       <c r="J76" s="130" t="n">
-        <v>107.034058846203</v>
+        <v>107.0340588462029</v>
       </c>
       <c r="K76" s="131" t="n">
         <v>28.64956631726437</v>
@@ -12530,7 +12530,7 @@
         <v>2397</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>0</v>
@@ -12539,13 +12539,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
@@ -12560,10 +12560,10 @@
         <v>2915.326833312611</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -12908,10 +12908,10 @@
         <v>9.932555049414749</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3180.836645549764</v>
+        <v>3180.836645549763</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>5357.161593511445</v>
+        <v>5357.161593511444</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13132,7 +13132,7 @@
         <v>32117</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>20536.86719694407</v>
+        <v>20536.86719694408</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>10920.07550760238</v>
@@ -13144,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>34569.77122015016</v>
+        <v>34569.77122015017</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>21715.48208383497</v>
@@ -13153,7 +13153,7 @@
         <v>11390.83898177362</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3431.616244730875</v>
+        <v>3431.616244730874</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>23374.6403171712</v>
       </c>
       <c r="W90" s="131" t="n">
-        <v>12044.16326397684</v>
+        <v>12044.16326397683</v>
       </c>
       <c r="X90" s="131" t="n">
         <v>3881.860491806206</v>
@@ -13174,7 +13174,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>39300.66407295424</v>
+        <v>39300.66407295423</v>
       </c>
     </row>
     <row r="91">
@@ -13266,10 +13266,10 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -13278,10 +13278,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N92" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>12.14013438652261</v>
@@ -13296,7 +13296,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V92" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W92" s="131" t="n">
         <v>8.002227321906959</v>
@@ -13305,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>144.6208709956583</v>
@@ -13406,7 +13406,7 @@
         <v>1013.803297948539</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>264.3214736883766</v>
+        <v>264.3214736883765</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -13418,10 +13418,10 @@
         <v>2624.318142957748</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>978.1421914832281</v>
+        <v>978.1421914832283</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>255.9861033440639</v>
+        <v>255.986103344064</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -13433,10 +13433,10 @@
         <v>2540.109190153185</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>939.3625222898573</v>
+        <v>939.3625222898575</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>246.5315273269332</v>
+        <v>246.5315273269333</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -13668,7 +13668,7 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>32.36265349002131</v>
@@ -13680,13 +13680,13 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>5.09858052922456</v>
@@ -13698,7 +13698,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>30.28909928964937</v>
@@ -13735,28 +13735,28 @@
         <v>20534</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5479.249428155606</v>
+        <v>5479.249428155599</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1629.268768588718</v>
+        <v>1629.268768588716</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>579.6662951627213</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>19682.11874075477</v>
+        <v>19682.11874075476</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>27370.30323266181</v>
+        <v>27370.3032326618</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>603.553380844643</v>
+        <v>603.5533808446444</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>21592.61987342794</v>
@@ -13765,19 +13765,19 @@
         <v>29613.85335450699</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6021.326513823606</v>
+        <v>6021.326513823602</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>23717.12306039543</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>32111.86101883307</v>
+        <v>32111.86101883306</v>
       </c>
     </row>
     <row r="100">
@@ -14086,7 +14086,7 @@
         <v>19690.79668663907</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>83149.83858095342</v>
+        <v>83149.83858095339</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>30269.455562463</v>
@@ -14104,7 +14104,7 @@
         <v>89020.12021794211</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>32116.05364128187</v>
+        <v>32116.05364128186</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>14764.98862398453</v>
@@ -14113,10 +14113,10 @@
         <v>4763.557007817432</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>23724.73996241635</v>
+        <v>23724.73996241634</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>96132.21220531575</v>
+        <v>96132.21220531574</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -16263,7 +16263,7 @@
         <v>1507482.658364703</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>195.7938686537839</v>
+        <v>195.7938686537838</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -17055,13 +17055,13 @@
         <v>11377.65923837764</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3422.487711428827</v>
+        <v>3422.487711428825</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36460.87458884433</v>
+        <v>36460.87458884434</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23326.03531108902</v>
@@ -17070,13 +17070,13 @@
         <v>12035.45165849652</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3876.170523329413</v>
+        <v>3876.170523329414</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>39237.65749291496</v>
+        <v>39237.65749291495</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -17361,10 +17361,10 @@
         <v>2594.410828881019</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>985.1537316312744</v>
+        <v>985.1537316312742</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.8945333813836</v>
+        <v>255.8945333813835</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -17376,10 +17376,10 @@
         <v>2524.098090035487</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.4907245728978</v>
+        <v>955.490724572898</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3325380336441</v>
+        <v>249.3325380336442</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -17391,16 +17391,16 @@
         <v>2448.763529811295</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>923.9759324905136</v>
+        <v>923.9759324905137</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>242.2889407543105</v>
+        <v>242.2889407543106</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.028403056119</v>
+        <v>3615.02840305612</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17682,7 +17682,7 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>32.36265349002131</v>
@@ -17694,13 +17694,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>5.09858052922456</v>
@@ -17712,7 +17712,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>30.28909928964937</v>
@@ -17763,10 +17763,10 @@
         <v>18137</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5479.249428155603</v>
+        <v>5479.249428155596</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1629.268768588716</v>
+        <v>1629.268768588714</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>579.6662951627213</v>
@@ -17775,31 +17775,31 @@
         <v>17013.70034841627</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>24701.88484032331</v>
+        <v>24701.8848403233</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>603.5533808446435</v>
+        <v>603.5533808446448</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>18677.29304011532</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>26698.52652119438</v>
+        <v>26698.52652119437</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6021.326513823609</v>
+        <v>6021.326513823606</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20543.90331686658</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>440033.7856706331</v>
+        <v>440033.7856706332</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>2143.165678765235</v>
@@ -18216,7 +18216,7 @@
         <v>20543.90331686658</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>90775.05061180433</v>
+        <v>90775.0506118043</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18463,10 +18463,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>89.47329720611964</v>
+        <v>89.47329720611963</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>54.7544447970989</v>
+        <v>54.75444479709891</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>13.17974339598205</v>
@@ -18484,7 +18484,7 @@
         <v>48.60500608217873</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>8.711605480314148</v>
+        <v>8.71160548031415</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>5.689968476792075</v>
@@ -18585,10 +18585,10 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -18597,10 +18597,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N74" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>12.14013438652261</v>
@@ -18615,7 +18615,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V74" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W74" s="131" t="n">
         <v>8.002227321906959</v>
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>144.6208709956583</v>
@@ -18719,7 +18719,7 @@
         <v>167</v>
       </c>
       <c r="J76" s="130" t="n">
-        <v>107.034058846203</v>
+        <v>107.0340588462029</v>
       </c>
       <c r="K76" s="131" t="n">
         <v>28.64956631726437</v>
@@ -19054,7 +19054,7 @@
         <v>2397</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>0</v>
@@ -19063,13 +19063,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
@@ -19084,10 +19084,10 @@
         <v>2915.326833312611</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -19432,10 +19432,10 @@
         <v>9.932555049414749</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3180.836645549764</v>
+        <v>3180.836645549763</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>5357.161593511445</v>
+        <v>5357.161593511444</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19656,7 +19656,7 @@
         <v>32117</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>20536.86719694407</v>
+        <v>20536.86719694408</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>10920.07550760238</v>
@@ -19668,7 +19668,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>34569.77122015016</v>
+        <v>34569.77122015017</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>21715.48208383497</v>
@@ -19677,7 +19677,7 @@
         <v>11390.83898177362</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3431.616244730875</v>
+        <v>3431.616244730874</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -19689,7 +19689,7 @@
         <v>23374.6403171712</v>
       </c>
       <c r="W90" s="131" t="n">
-        <v>12044.16326397684</v>
+        <v>12044.16326397683</v>
       </c>
       <c r="X90" s="131" t="n">
         <v>3881.860491806206</v>
@@ -19698,7 +19698,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>39300.66407295424</v>
+        <v>39300.66407295423</v>
       </c>
     </row>
     <row r="91">
@@ -19790,10 +19790,10 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -19802,10 +19802,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N92" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>12.14013438652261</v>
@@ -19820,7 +19820,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V92" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W92" s="131" t="n">
         <v>8.002227321906959</v>
@@ -19829,7 +19829,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>144.6208709956583</v>
@@ -19930,7 +19930,7 @@
         <v>1013.803297948539</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>264.3214736883766</v>
+        <v>264.3214736883765</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -19942,10 +19942,10 @@
         <v>2624.318142957748</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>978.1421914832281</v>
+        <v>978.1421914832283</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>255.9861033440639</v>
+        <v>255.986103344064</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -19957,10 +19957,10 @@
         <v>2540.109190153185</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>939.3625222898573</v>
+        <v>939.3625222898575</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>246.5315273269332</v>
+        <v>246.5315273269333</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>32.36265349002131</v>
@@ -20204,13 +20204,13 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>5.09858052922456</v>
@@ -20222,7 +20222,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>30.28909928964937</v>
@@ -20259,28 +20259,28 @@
         <v>20534</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5479.249428155606</v>
+        <v>5479.249428155599</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1629.268768588718</v>
+        <v>1629.268768588716</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>579.6662951627213</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>19682.11874075477</v>
+        <v>19682.11874075476</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>27370.30323266181</v>
+        <v>27370.3032326618</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>603.553380844643</v>
+        <v>603.5533808446444</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>21592.61987342794</v>
@@ -20289,19 +20289,19 @@
         <v>29613.85335450699</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6021.326513823606</v>
+        <v>6021.326513823602</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>23717.12306039543</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>32111.86101883307</v>
+        <v>32111.86101883306</v>
       </c>
     </row>
     <row r="100">
@@ -20610,7 +20610,7 @@
         <v>19690.79668663907</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>83149.83858095342</v>
+        <v>83149.83858095339</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>30269.455562463</v>
@@ -20628,7 +20628,7 @@
         <v>89020.12021794211</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>32116.05364128187</v>
+        <v>32116.05364128186</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>14764.98862398453</v>
@@ -20637,10 +20637,10 @@
         <v>4763.557007817432</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>23724.73996241635</v>
+        <v>23724.73996241634</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>96132.21220531575</v>
+        <v>96132.21220531574</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55719460.42474838</v>
+        <v>55719460.42474837</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379245</v>
+        <v>68660.92484379247</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21830,7 +21830,7 @@
         <v>11122925.05977617</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>13115.78537471264</v>
+        <v>13115.78537471265</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>2918129.028513301</v>
+        <v>2918129.028513302</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22503,7 +22503,7 @@
         <v>2055912.083175347</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>4563.755983610184</v>
+        <v>4563.755983610183</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2029241.191294712</v>
+        <v>2029241.191294711</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>3570.123843302602</v>
@@ -22657,7 +22657,7 @@
         <v>1963455.430630518</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>2764.956425043127</v>
+        <v>2764.956425043126</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -23579,13 +23579,13 @@
         <v>11377.65923837764</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3422.487711428827</v>
+        <v>3422.487711428825</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36460.87458884433</v>
+        <v>36460.87458884434</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23326.03531108902</v>
@@ -23594,13 +23594,13 @@
         <v>12035.45165849652</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3876.170523329413</v>
+        <v>3876.170523329414</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>39237.65749291496</v>
+        <v>39237.65749291495</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>4027563.801922101</v>
+        <v>4027563.8019221</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>0</v>
@@ -23885,10 +23885,10 @@
         <v>2594.410828881019</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>985.1537316312744</v>
+        <v>985.1537316312742</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.8945333813836</v>
+        <v>255.8945333813835</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -23900,10 +23900,10 @@
         <v>2524.098090035487</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.4907245728978</v>
+        <v>955.490724572898</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3325380336441</v>
+        <v>249.3325380336442</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -23915,16 +23915,16 @@
         <v>2448.763529811295</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>923.9759324905136</v>
+        <v>923.9759324905137</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>242.2889407543105</v>
+        <v>242.2889407543106</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.028403056119</v>
+        <v>3615.02840305612</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1261835.258461665</v>
+        <v>1261835.258461664</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>1090.285175587757</v>
@@ -24206,7 +24206,7 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>32.36265349002131</v>
@@ -24218,13 +24218,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>5.09858052922456</v>
@@ -24236,7 +24236,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>30.28909928964937</v>
@@ -24287,10 +24287,10 @@
         <v>18137</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5479.249428155603</v>
+        <v>5479.249428155596</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1629.268768588716</v>
+        <v>1629.268768588714</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>579.6662951627213</v>
@@ -24299,31 +24299,31 @@
         <v>17013.70034841627</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>24701.88484032331</v>
+        <v>24701.8848403233</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>603.5533808446435</v>
+        <v>603.5533808446448</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>18677.29304011532</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>26698.52652119438</v>
+        <v>26698.52652119437</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6021.326513823609</v>
+        <v>6021.326513823606</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20543.90331686658</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24510,7 +24510,7 @@
         <v>412584.2450424845</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>765.5601426828616</v>
+        <v>765.5601426828617</v>
       </c>
     </row>
     <row r="66">
@@ -24673,7 +24673,7 @@
         <v>334190.0867178393</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>913.0841014375314</v>
+        <v>913.0841014375313</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24740,7 +24740,7 @@
         <v>20543.90331686658</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>90775.05061180433</v>
+        <v>90775.0506118043</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -24987,10 +24987,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>89.47329720611964</v>
+        <v>89.47329720611963</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>54.7544447970989</v>
+        <v>54.75444479709891</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>13.17974339598205</v>
@@ -25008,7 +25008,7 @@
         <v>48.60500608217873</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>8.711605480314148</v>
+        <v>8.71160548031415</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>5.689968476792075</v>
@@ -25109,10 +25109,10 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -25121,10 +25121,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N74" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>12.14013438652261</v>
@@ -25139,7 +25139,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V74" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W74" s="131" t="n">
         <v>8.002227321906959</v>
@@ -25148,7 +25148,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>144.6208709956583</v>
@@ -25243,7 +25243,7 @@
         <v>167</v>
       </c>
       <c r="J76" s="130" t="n">
-        <v>107.034058846203</v>
+        <v>107.0340588462029</v>
       </c>
       <c r="K76" s="131" t="n">
         <v>28.64956631726437</v>
@@ -25578,7 +25578,7 @@
         <v>2397</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>0</v>
@@ -25587,13 +25587,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>2915.326833312611</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -25956,10 +25956,10 @@
         <v>9.932555049414749</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3180.836645549764</v>
+        <v>3180.836645549763</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>5357.161593511445</v>
+        <v>5357.161593511444</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26180,7 +26180,7 @@
         <v>32117</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>20536.86719694407</v>
+        <v>20536.86719694408</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>10920.07550760238</v>
@@ -26192,7 +26192,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>34569.77122015016</v>
+        <v>34569.77122015017</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>21715.48208383497</v>
@@ -26201,7 +26201,7 @@
         <v>11390.83898177362</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3431.616244730875</v>
+        <v>3431.616244730874</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -26213,7 +26213,7 @@
         <v>23374.6403171712</v>
       </c>
       <c r="W90" s="131" t="n">
-        <v>12044.16326397684</v>
+        <v>12044.16326397683</v>
       </c>
       <c r="X90" s="131" t="n">
         <v>3881.860491806206</v>
@@ -26222,7 +26222,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>39300.66407295424</v>
+        <v>39300.66407295423</v>
       </c>
     </row>
     <row r="91">
@@ -26314,10 +26314,10 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -26326,10 +26326,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N92" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>12.14013438652261</v>
@@ -26344,7 +26344,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V92" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W92" s="131" t="n">
         <v>8.002227321906959</v>
@@ -26353,7 +26353,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>144.6208709956583</v>
@@ -26454,7 +26454,7 @@
         <v>1013.803297948539</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>264.3214736883766</v>
+        <v>264.3214736883765</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -26466,10 +26466,10 @@
         <v>2624.318142957748</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>978.1421914832281</v>
+        <v>978.1421914832283</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>255.9861033440639</v>
+        <v>255.986103344064</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -26481,10 +26481,10 @@
         <v>2540.109190153185</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>939.3625222898573</v>
+        <v>939.3625222898575</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>246.5315273269332</v>
+        <v>246.5315273269333</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -26716,7 +26716,7 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>32.36265349002131</v>
@@ -26728,13 +26728,13 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>5.09858052922456</v>
@@ -26746,7 +26746,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>30.28909928964937</v>
@@ -26783,28 +26783,28 @@
         <v>20534</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5479.249428155606</v>
+        <v>5479.249428155599</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1629.268768588718</v>
+        <v>1629.268768588716</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>579.6662951627213</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>19682.11874075477</v>
+        <v>19682.11874075476</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>27370.30323266181</v>
+        <v>27370.3032326618</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>603.553380844643</v>
+        <v>603.5533808446444</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>21592.61987342794</v>
@@ -26813,19 +26813,19 @@
         <v>29613.85335450699</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6021.326513823606</v>
+        <v>6021.326513823602</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>23717.12306039543</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>32111.86101883307</v>
+        <v>32111.86101883306</v>
       </c>
     </row>
     <row r="100">
@@ -27134,7 +27134,7 @@
         <v>19690.79668663907</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>83149.83858095342</v>
+        <v>83149.83858095339</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>30269.455562463</v>
@@ -27152,7 +27152,7 @@
         <v>89020.12021794211</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>32116.05364128187</v>
+        <v>32116.05364128186</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>14764.98862398453</v>
@@ -27161,10 +27161,10 @@
         <v>4763.557007817432</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>23724.73996241635</v>
+        <v>23724.73996241634</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>96132.21220531575</v>
+        <v>96132.21220531574</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28200,7 +28200,7 @@
         <v>69285584.18914482</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>17597343.42452664</v>
+        <v>17597343.42452665</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>5298947.526429203</v>
+        <v>5298947.526429204</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>0</v>
@@ -29104,7 +29104,7 @@
         <v>2261110.921757242</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>2957.226786839573</v>
+        <v>2957.226786839574</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1704572.018423962</v>
+        <v>1704572.018423963</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1964.648020269053</v>
@@ -29311,7 +29311,7 @@
         <v>1628208.049291219</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>2218.827294049512</v>
+        <v>2218.827294049513</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -30103,13 +30103,13 @@
         <v>11377.65923837764</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>3422.487711428827</v>
+        <v>3422.487711428825</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>36460.87458884433</v>
+        <v>36460.87458884434</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>23326.03531108902</v>
@@ -30118,13 +30118,13 @@
         <v>12035.45165849652</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>3876.170523329413</v>
+        <v>3876.170523329414</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="132" t="n">
-        <v>39237.65749291496</v>
+        <v>39237.65749291495</v>
       </c>
       <c r="AE54" s="121" t="n">
         <v>6</v>
@@ -30409,10 +30409,10 @@
         <v>2594.410828881019</v>
       </c>
       <c r="K58" s="131" t="n">
-        <v>985.1537316312744</v>
+        <v>985.1537316312742</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>255.8945333813836</v>
+        <v>255.8945333813835</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -30424,10 +30424,10 @@
         <v>2524.098090035487</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>955.4907245728978</v>
+        <v>955.490724572898</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>249.3325380336441</v>
+        <v>249.3325380336442</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
@@ -30439,16 +30439,16 @@
         <v>2448.763529811295</v>
       </c>
       <c r="W58" s="131" t="n">
-        <v>923.9759324905136</v>
+        <v>923.9759324905137</v>
       </c>
       <c r="X58" s="131" t="n">
-        <v>242.2889407543105</v>
+        <v>242.2889407543106</v>
       </c>
       <c r="Y58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>3615.028403056119</v>
+        <v>3615.02840305612</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>987932.216631648</v>
+        <v>987932.2166316478</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>557.5626950911861</v>
@@ -30730,7 +30730,7 @@
         <v>350</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K62" s="131" t="n">
         <v>32.36265349002131</v>
@@ -30742,13 +30742,13 @@
         <v>0</v>
       </c>
       <c r="N62" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P62" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>5.09858052922456</v>
@@ -30760,7 +30760,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>30.28909928964937</v>
@@ -30811,10 +30811,10 @@
         <v>18137</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5479.249428155603</v>
+        <v>5479.249428155596</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1629.268768588716</v>
+        <v>1629.268768588714</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>579.6662951627213</v>
@@ -30823,31 +30823,31 @@
         <v>17013.70034841627</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>24701.88484032331</v>
+        <v>24701.8848403233</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>603.5533808446435</v>
+        <v>603.5533808446448</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>18677.29304011532</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>26698.52652119438</v>
+        <v>26698.52652119437</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>6021.326513823609</v>
+        <v>6021.326513823606</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y63" s="131" t="n">
         <v>20543.90331686658</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>18897.53340758179</v>
+        <v>18897.53340758178</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>585780.5644306375</v>
+        <v>585780.5644306374</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2625.902308392545</v>
@@ -31264,7 +31264,7 @@
         <v>20543.90331686658</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>90775.05061180433</v>
+        <v>90775.0506118043</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31278,7 +31278,7 @@
         <v>262049.9006640031</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>71.94315107435395</v>
+        <v>71.94315107435393</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -31511,10 +31511,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>89.47329720611964</v>
+        <v>89.47329720611963</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>54.7544447970989</v>
+        <v>54.75444479709891</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>13.17974339598205</v>
@@ -31532,7 +31532,7 @@
         <v>48.60500608217873</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>8.711605480314148</v>
+        <v>8.71160548031415</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>5.689968476792075</v>
@@ -31633,10 +31633,10 @@
         <v>186</v>
       </c>
       <c r="J74" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K74" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L74" s="131" t="n">
         <v>0</v>
@@ -31645,10 +31645,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N74" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P74" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q74" s="131" t="n">
         <v>12.14013438652261</v>
@@ -31663,7 +31663,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V74" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W74" s="131" t="n">
         <v>8.002227321906959</v>
@@ -31672,7 +31672,7 @@
         <v>0</v>
       </c>
       <c r="Y74" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z74" s="132" t="n">
         <v>144.6208709956583</v>
@@ -31767,7 +31767,7 @@
         <v>167</v>
       </c>
       <c r="J76" s="130" t="n">
-        <v>107.034058846203</v>
+        <v>107.0340588462029</v>
       </c>
       <c r="K76" s="131" t="n">
         <v>28.64956631726437</v>
@@ -32102,7 +32102,7 @@
         <v>2397</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>0</v>
@@ -32111,13 +32111,13 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2668.418392338495</v>
+        <v>2668.418392338496</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>0</v>
@@ -32132,10 +32132,10 @@
         <v>2915.326833312611</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -32480,10 +32480,10 @@
         <v>9.932555049414749</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>3180.836645549764</v>
+        <v>3180.836645549763</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>5357.161593511445</v>
+        <v>5357.161593511444</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32704,7 +32704,7 @@
         <v>32117</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>20536.86719694407</v>
+        <v>20536.86719694408</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>10920.07550760238</v>
@@ -32716,7 +32716,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>34569.77122015016</v>
+        <v>34569.77122015017</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>21715.48208383497</v>
@@ -32725,7 +32725,7 @@
         <v>11390.83898177362</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>3431.616244730875</v>
+        <v>3431.616244730874</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -32737,7 +32737,7 @@
         <v>23374.6403171712</v>
       </c>
       <c r="W90" s="131" t="n">
-        <v>12044.16326397684</v>
+        <v>12044.16326397683</v>
       </c>
       <c r="X90" s="131" t="n">
         <v>3881.860491806206</v>
@@ -32746,7 +32746,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>39300.66407295424</v>
+        <v>39300.66407295423</v>
       </c>
     </row>
     <row r="91">
@@ -32838,10 +32838,10 @@
         <v>186</v>
       </c>
       <c r="J92" s="130" t="n">
-        <v>144.1175339064627</v>
+        <v>144.1175339064626</v>
       </c>
       <c r="K92" s="131" t="n">
-        <v>15.89356319143109</v>
+        <v>15.89356319143108</v>
       </c>
       <c r="L92" s="131" t="n">
         <v>0</v>
@@ -32850,10 +32850,10 @@
         <v>8.677945884309336</v>
       </c>
       <c r="N92" s="132" t="n">
-        <v>168.6890429822031</v>
+        <v>168.689042982203</v>
       </c>
       <c r="P92" s="130" t="n">
-        <v>137.9660640772047</v>
+        <v>137.9660640772048</v>
       </c>
       <c r="Q92" s="131" t="n">
         <v>12.14013438652261</v>
@@ -32868,7 +32868,7 @@
         <v>158.2054900284876</v>
       </c>
       <c r="V92" s="130" t="n">
-        <v>129.0017416528368</v>
+        <v>129.0017416528367</v>
       </c>
       <c r="W92" s="131" t="n">
         <v>8.002227321906959</v>
@@ -32877,7 +32877,7 @@
         <v>0</v>
       </c>
       <c r="Y92" s="131" t="n">
-        <v>7.616902020914613</v>
+        <v>7.616902020914612</v>
       </c>
       <c r="Z92" s="132" t="n">
         <v>144.6208709956583</v>
@@ -32978,7 +32978,7 @@
         <v>1013.803297948539</v>
       </c>
       <c r="L94" s="131" t="n">
-        <v>264.3214736883766</v>
+        <v>264.3214736883765</v>
       </c>
       <c r="M94" s="131" t="n">
         <v>0</v>
@@ -32990,10 +32990,10 @@
         <v>2624.318142957748</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>978.1421914832281</v>
+        <v>978.1421914832283</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>255.9861033440639</v>
+        <v>255.986103344064</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -33005,10 +33005,10 @@
         <v>2540.109190153185</v>
       </c>
       <c r="W94" s="131" t="n">
-        <v>939.3625222898573</v>
+        <v>939.3625222898575</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>246.5315273269332</v>
+        <v>246.5315273269333</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -33240,7 +33240,7 @@
         <v>350</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>54.4648845376473</v>
+        <v>54.46488453764731</v>
       </c>
       <c r="K98" s="131" t="n">
         <v>32.36265349002131</v>
@@ -33252,13 +33252,13 @@
         <v>0</v>
       </c>
       <c r="N98" s="132" t="n">
-        <v>92.08976625848064</v>
+        <v>92.08976625848065</v>
       </c>
       <c r="P98" s="130" t="n">
         <v>52.77150672502631</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>31.35623740589778</v>
+        <v>31.35623740589779</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>5.09858052922456</v>
@@ -33270,7 +33270,7 @@
         <v>89.22632466014866</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>50.97587848104049</v>
+        <v>50.97587848104048</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>30.28909928964937</v>
@@ -33307,28 +33307,28 @@
         <v>20534</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>5479.249428155606</v>
+        <v>5479.249428155599</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1629.268768588718</v>
+        <v>1629.268768588716</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>579.6662951627213</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>19682.11874075477</v>
+        <v>19682.11874075476</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>27370.30323266181</v>
+        <v>27370.3032326618</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>5738.917764868052</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>1678.762335366355</v>
+        <v>1678.762335366351</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>603.553380844643</v>
+        <v>603.5533808446444</v>
       </c>
       <c r="S99" s="131" t="n">
         <v>21592.61987342794</v>
@@ -33337,19 +33337,19 @@
         <v>29613.85335450699</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6021.326513823606</v>
+        <v>6021.326513823602</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>1743.171511106273</v>
+        <v>1743.171511106277</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>630.2399335077571</v>
+        <v>630.2399335077562</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>23717.12306039543</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>32111.86101883307</v>
+        <v>32111.86101883306</v>
       </c>
     </row>
     <row r="100">
@@ -33658,7 +33658,7 @@
         <v>19690.79668663907</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>83149.83858095342</v>
+        <v>83149.83858095339</v>
       </c>
       <c r="P104" s="142" t="n">
         <v>30269.455562463</v>
@@ -33676,7 +33676,7 @@
         <v>89020.12021794211</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>32116.05364128187</v>
+        <v>32116.05364128186</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>14764.98862398453</v>
@@ -33685,10 +33685,10 @@
         <v>4763.557007817432</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>23724.73996241635</v>
+        <v>23724.73996241634</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>96132.21220531575</v>
+        <v>96132.21220531574</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
